--- a/data/Liga Betplay 2026.xlsx
+++ b/data/Liga Betplay 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luisalejandrorestrepo/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luisalejandrorestrepo/Desktop/Streamlit Team App/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03212CE0-98BD-E640-A266-57961C6C778D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA712FB-CBF3-F14C-B384-B0288847CF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16760" xr2:uid="{55647C75-A5AD-C94E-944A-A5D94B9EDCEA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>Goles</t>
   </si>
@@ -95,15 +95,6 @@
     <t>PPDA</t>
   </si>
   <si>
-    <t>Tiros al arco</t>
-  </si>
-  <si>
-    <t>% Tiros al arco</t>
-  </si>
-  <si>
-    <t>Tiros</t>
-  </si>
-  <si>
     <t>Pases Acertados</t>
   </si>
   <si>
@@ -144,15 +135,6 @@
   </si>
   <si>
     <t>% Duelos Ganados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiros de fuera del área </t>
-  </si>
-  <si>
-    <t>Tiros de fuera del área al arco</t>
-  </si>
-  <si>
-    <t>% Tiros de fuera del área al arco</t>
   </si>
   <si>
     <t>Ataques posicionales</t>
@@ -397,12 +379,70 @@
   <si>
     <t>Teams</t>
   </si>
+  <si>
+    <t>Non Penalty xG</t>
+  </si>
+  <si>
+    <t>Non Penalty xG_Rival</t>
+  </si>
+  <si>
+    <t>Goles-Goles Esperados</t>
+  </si>
+  <si>
+    <t>Goles en Contra - Goles Esperados en Contra</t>
+  </si>
+  <si>
+    <t>Remates dentro del Area</t>
+  </si>
+  <si>
+    <t>Remates dentro del Area_Rival</t>
+  </si>
+  <si>
+    <t>% Recuperaciones Bajas</t>
+  </si>
+  <si>
+    <t>% Recuperaciones Medias</t>
+  </si>
+  <si>
+    <t>% Recuperaciones Altas</t>
+  </si>
+  <si>
+    <t>xG por Remate</t>
+  </si>
+  <si>
+    <t>xG por Remate_Rival</t>
+  </si>
+  <si>
+    <t>Remates</t>
+  </si>
+  <si>
+    <t>Remates al arco</t>
+  </si>
+  <si>
+    <t>% Remates al arco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remates de fuera del área </t>
+  </si>
+  <si>
+    <t>Remates de fuera del área al arco</t>
+  </si>
+  <si>
+    <t>% Remates de fuera del área al arco</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -428,15 +468,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -768,15 +811,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB93FC8-8389-2B4E-9C7F-964071352BBA}">
-  <dimension ref="A1:GQ21"/>
+  <dimension ref="A1:HB21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -785,130 +828,130 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" t="s">
-        <v>23</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
       </c>
       <c r="K1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>29</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>31</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>32</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
+        <v>128</v>
+      </c>
+      <c r="W1" t="s">
+        <v>129</v>
+      </c>
+      <c r="X1" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y1" t="s">
         <v>33</v>
       </c>
-      <c r="T1" t="s">
+      <c r="Z1" t="s">
         <v>34</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AA1" t="s">
         <v>35</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AB1" t="s">
         <v>36</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AC1" t="s">
         <v>37</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AD1" t="s">
         <v>38</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AE1" t="s">
         <v>39</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AF1" t="s">
         <v>40</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AG1" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AH1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI1" t="s">
         <v>42</v>
       </c>
-      <c r="AC1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD1" t="s">
+      <c r="AJ1" t="s">
         <v>44</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AK1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL1" t="s">
         <v>45</v>
       </c>
-      <c r="AF1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AM1" t="s">
         <v>47</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AN1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO1" t="s">
         <v>49</v>
       </c>
-      <c r="AI1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ1" t="s">
+      <c r="AP1" t="s">
         <v>50</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AQ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AR1" t="s">
         <v>52</v>
       </c>
-      <c r="AL1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM1" t="s">
+      <c r="AS1" t="s">
         <v>53</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>59</v>
       </c>
       <c r="AT1" t="s">
         <v>3</v>
@@ -917,55 +960,55 @@
         <v>4</v>
       </c>
       <c r="AV1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="AW1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AX1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AY1" t="s">
         <v>5</v>
       </c>
       <c r="AZ1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BA1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="BB1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="BC1" t="s">
         <v>6</v>
       </c>
       <c r="BD1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BJ1" t="s">
         <v>67</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BK1" t="s">
         <v>66</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BL1" t="s">
         <v>68</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>74</v>
       </c>
       <c r="BM1" t="s">
         <v>7</v>
@@ -983,76 +1026,76 @@
         <v>11</v>
       </c>
       <c r="BR1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" t="s">
         <v>76</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BY1" t="s">
         <v>75</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BZ1" t="s">
         <v>77</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="CA1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" t="s">
         <v>79</v>
       </c>
-      <c r="BV1" t="s">
-        <v>78</v>
-      </c>
-      <c r="BW1" t="s">
+      <c r="CC1" t="s">
         <v>80</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="CD1" t="s">
         <v>82</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="CE1" t="s">
         <v>81</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CF1" t="s">
         <v>83</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CG1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CH1" t="s">
         <v>84</v>
       </c>
-      <c r="CB1" t="s">
-        <v>85</v>
-      </c>
-      <c r="CC1" t="s">
+      <c r="CI1" t="s">
         <v>86</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CJ1" t="s">
         <v>88</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CK1" t="s">
         <v>87</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CL1" t="s">
         <v>89</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CM1" t="s">
         <v>91</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CN1" t="s">
         <v>90</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CO1" t="s">
         <v>92</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>95</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>97</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>96</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>98</v>
       </c>
       <c r="CP1" t="s">
         <v>12</v>
@@ -1085,15 +1128,15 @@
       </c>
       <c r="CY1" t="str">
         <f t="shared" si="0"/>
-        <v>Tiros_rival</v>
+        <v>Remates_rival</v>
       </c>
       <c r="CZ1" t="str">
         <f t="shared" si="0"/>
-        <v>Tiros al arco_rival</v>
+        <v>Remates al arco_rival</v>
       </c>
       <c r="DA1" t="str">
         <f t="shared" si="0"/>
-        <v>% Tiros al arco_rival</v>
+        <v>% Remates al arco_rival</v>
       </c>
       <c r="DB1" t="str">
         <f t="shared" si="0"/>
@@ -1157,15 +1200,15 @@
       </c>
       <c r="DQ1" t="str">
         <f t="shared" si="0"/>
-        <v>Tiros de fuera del área _rival</v>
+        <v>Remates de fuera del área _rival</v>
       </c>
       <c r="DR1" t="str">
         <f t="shared" si="0"/>
-        <v>Tiros de fuera del área al arco_rival</v>
+        <v>Remates de fuera del área al arco_rival</v>
       </c>
       <c r="DS1" t="str">
         <f t="shared" si="0"/>
-        <v>% Tiros de fuera del área al arco_rival</v>
+        <v>% Remates de fuera del área al arco_rival</v>
       </c>
       <c r="DT1" t="str">
         <f t="shared" si="0"/>
@@ -1471,10 +1514,43 @@
         <f t="shared" ref="GQ1" si="24">CV1&amp;"_rival"</f>
         <v>PPDA_rival</v>
       </c>
+      <c r="GR1" t="s">
+        <v>114</v>
+      </c>
+      <c r="GS1" t="s">
+        <v>115</v>
+      </c>
+      <c r="GT1" t="s">
+        <v>116</v>
+      </c>
+      <c r="GU1" t="s">
+        <v>117</v>
+      </c>
+      <c r="GV1" t="s">
+        <v>118</v>
+      </c>
+      <c r="GW1" t="s">
+        <v>119</v>
+      </c>
+      <c r="GX1" t="s">
+        <v>120</v>
+      </c>
+      <c r="GY1" t="s">
+        <v>121</v>
+      </c>
+      <c r="GZ1" t="s">
+        <v>122</v>
+      </c>
+      <c r="HA1" t="s">
+        <v>123</v>
+      </c>
+      <c r="HB1" t="s">
+        <v>124</v>
+      </c>
     </row>
-    <row r="2" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B2">
         <v>1.2857142857142858</v>
@@ -2070,10 +2146,54 @@
       <c r="GQ2">
         <v>11.51</v>
       </c>
+      <c r="GR2">
+        <f>C2- (AN2*0.76)</f>
+        <v>1.337142857142857</v>
+      </c>
+      <c r="GS2">
+        <f>CX2-(EI2*0.76)</f>
+        <v>0.84428571428571431</v>
+      </c>
+      <c r="GT2">
+        <f>B2-C2</f>
+        <v>-5.1428571428571157E-2</v>
+      </c>
+      <c r="GU2">
+        <f>CW2-CX2</f>
+        <v>8.1428571428571406E-2</v>
+      </c>
+      <c r="GV2">
+        <f>D2-V2</f>
+        <v>6.5714285714285712</v>
+      </c>
+      <c r="GW2">
+        <f>CY2-DQ2</f>
+        <v>5.1428571428571423</v>
+      </c>
+      <c r="GX2" s="2">
+        <f>P2/O2</f>
+        <v>0.48994515539305306</v>
+      </c>
+      <c r="GY2" s="2">
+        <f>Q2/O2</f>
+        <v>0.36014625228519198</v>
+      </c>
+      <c r="GZ2" s="2">
+        <f>R2/O2</f>
+        <v>0.14990859232175502</v>
+      </c>
+      <c r="HA2">
+        <f>C2/D2</f>
+        <v>0.11555555555555554</v>
+      </c>
+      <c r="HB2">
+        <f>CX2/CY2</f>
+        <v>8.7411764705882355E-2</v>
+      </c>
     </row>
-    <row r="3" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B3">
         <v>0.42857142857142855</v>
@@ -2669,10 +2789,54 @@
       <c r="GQ3">
         <v>12.475714285714286</v>
       </c>
+      <c r="GR3">
+        <f t="shared" ref="GR3:GR21" si="25">C3- (AN3*0.76)</f>
+        <v>0.75</v>
+      </c>
+      <c r="GS3">
+        <f t="shared" ref="GS3:GS21" si="26">CX3-(EI3*0.76)</f>
+        <v>0.94857142857142862</v>
+      </c>
+      <c r="GT3">
+        <f t="shared" ref="GT3:GT21" si="27">B3-C3</f>
+        <v>-0.32142857142857145</v>
+      </c>
+      <c r="GU3">
+        <f t="shared" ref="GU3:GU21" si="28">CW3-CX3</f>
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="GV3">
+        <f t="shared" ref="GV3:GV21" si="29">D3-V3</f>
+        <v>4.7142857142857153</v>
+      </c>
+      <c r="GW3">
+        <f t="shared" ref="GW3:GW21" si="30">CY3-DQ3</f>
+        <v>4.4285714285714279</v>
+      </c>
+      <c r="GX3" s="2">
+        <f t="shared" ref="GX3:GX21" si="31">P3/O3</f>
+        <v>0.42912621359223302</v>
+      </c>
+      <c r="GY3" s="2">
+        <f t="shared" ref="GY3:GY21" si="32">Q3/O3</f>
+        <v>0.42330097087378643</v>
+      </c>
+      <c r="GZ3" s="2">
+        <f t="shared" ref="GZ3:GZ21" si="33">R3/O3</f>
+        <v>0.14757281553398061</v>
+      </c>
+      <c r="HA3">
+        <f t="shared" ref="HA3:HA21" si="34">C3/D3</f>
+        <v>6.6455696202531639E-2</v>
+      </c>
+      <c r="HB3">
+        <f t="shared" ref="HB3:HB21" si="35">CX3/CY3</f>
+        <v>0.12000000000000001</v>
+      </c>
     </row>
-    <row r="4" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B4">
         <v>1.5714285714285714</v>
@@ -3268,10 +3432,54 @@
       <c r="GQ4">
         <v>14.492857142857142</v>
       </c>
+      <c r="GR4">
+        <f t="shared" si="25"/>
+        <v>0.95571428571428596</v>
+      </c>
+      <c r="GS4">
+        <f t="shared" si="26"/>
+        <v>0.96857142857142864</v>
+      </c>
+      <c r="GT4">
+        <f t="shared" si="27"/>
+        <v>0.39857142857142835</v>
+      </c>
+      <c r="GU4">
+        <f t="shared" si="28"/>
+        <v>-0.47142857142857142</v>
+      </c>
+      <c r="GV4">
+        <f t="shared" si="29"/>
+        <v>5</v>
+      </c>
+      <c r="GW4">
+        <f t="shared" si="30"/>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="GX4" s="2">
+        <f t="shared" si="31"/>
+        <v>0.46076458752515093</v>
+      </c>
+      <c r="GY4" s="2">
+        <f t="shared" si="32"/>
+        <v>0.3782696177062374</v>
+      </c>
+      <c r="GZ4" s="2">
+        <f t="shared" si="33"/>
+        <v>0.16096579476861167</v>
+      </c>
+      <c r="HA4">
+        <f t="shared" si="34"/>
+        <v>9.0219780219780235E-2</v>
+      </c>
+      <c r="HB4">
+        <f t="shared" si="35"/>
+        <v>0.11527777777777777</v>
+      </c>
     </row>
-    <row r="5" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B5">
         <v>1.4285714285714286</v>
@@ -3867,10 +4075,54 @@
       <c r="GQ5">
         <v>10.631428571428572</v>
       </c>
+      <c r="GR5">
+        <f t="shared" si="25"/>
+        <v>0.98428571428571421</v>
+      </c>
+      <c r="GS5">
+        <f t="shared" si="26"/>
+        <v>0.45</v>
+      </c>
+      <c r="GT5">
+        <f t="shared" si="27"/>
+        <v>0.44428571428571439</v>
+      </c>
+      <c r="GU5">
+        <f t="shared" si="28"/>
+        <v>0.12142857142857139</v>
+      </c>
+      <c r="GV5">
+        <f t="shared" si="29"/>
+        <v>5.5714285714285712</v>
+      </c>
+      <c r="GW5">
+        <f t="shared" si="30"/>
+        <v>2.4285714285714288</v>
+      </c>
+      <c r="GX5" s="2">
+        <f t="shared" si="31"/>
+        <v>0.3941605839416058</v>
+      </c>
+      <c r="GY5" s="2">
+        <f t="shared" si="32"/>
+        <v>0.45620437956204379</v>
+      </c>
+      <c r="GZ5" s="2">
+        <f t="shared" si="33"/>
+        <v>0.14963503649635035</v>
+      </c>
+      <c r="HA5">
+        <f t="shared" si="34"/>
+        <v>9.3108108108108101E-2</v>
+      </c>
+      <c r="HB5">
+        <f t="shared" si="35"/>
+        <v>5.8333333333333334E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B6">
         <v>2.6</v>
@@ -4466,10 +4718,54 @@
       <c r="GQ6">
         <v>15.203999999999999</v>
       </c>
+      <c r="GR6">
+        <f t="shared" si="25"/>
+        <v>2.3719999999999999</v>
+      </c>
+      <c r="GS6">
+        <f t="shared" si="26"/>
+        <v>0.91999999999999993</v>
+      </c>
+      <c r="GT6">
+        <f t="shared" si="27"/>
+        <v>-7.6000000000000068E-2</v>
+      </c>
+      <c r="GU6">
+        <f t="shared" si="28"/>
+        <v>-0.31999999999999995</v>
+      </c>
+      <c r="GV6">
+        <f t="shared" si="29"/>
+        <v>11.200000000000001</v>
+      </c>
+      <c r="GW6">
+        <f t="shared" si="30"/>
+        <v>5.2</v>
+      </c>
+      <c r="GX6" s="2">
+        <f t="shared" si="31"/>
+        <v>0.4212121212121212</v>
+      </c>
+      <c r="GY6" s="2">
+        <f t="shared" si="32"/>
+        <v>0.44848484848484849</v>
+      </c>
+      <c r="GZ6" s="2">
+        <f t="shared" si="33"/>
+        <v>0.13030303030303031</v>
+      </c>
+      <c r="HA6">
+        <f t="shared" si="34"/>
+        <v>0.15033707865168539</v>
+      </c>
+      <c r="HB6">
+        <f t="shared" si="35"/>
+        <v>9.7872340425531903E-2</v>
+      </c>
     </row>
-    <row r="7" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B7">
         <v>0.875</v>
@@ -5065,10 +5361,54 @@
       <c r="GQ7">
         <v>9.2462499999999999</v>
       </c>
+      <c r="GR7">
+        <f t="shared" si="25"/>
+        <v>0.55624999999999991</v>
+      </c>
+      <c r="GS7">
+        <f t="shared" si="26"/>
+        <v>1.3112500000000002</v>
+      </c>
+      <c r="GT7">
+        <f t="shared" si="27"/>
+        <v>0.31875000000000009</v>
+      </c>
+      <c r="GU7">
+        <f t="shared" si="28"/>
+        <v>0.21874999999999978</v>
+      </c>
+      <c r="GV7">
+        <f t="shared" si="29"/>
+        <v>2.5</v>
+      </c>
+      <c r="GW7">
+        <f t="shared" si="30"/>
+        <v>6.625</v>
+      </c>
+      <c r="GX7" s="2">
+        <f t="shared" si="31"/>
+        <v>0.48310810810810811</v>
+      </c>
+      <c r="GY7" s="2">
+        <f t="shared" si="32"/>
+        <v>0.41047297297297297</v>
+      </c>
+      <c r="GZ7" s="2">
+        <f t="shared" si="33"/>
+        <v>0.10641891891891891</v>
+      </c>
+      <c r="HA7">
+        <f t="shared" si="34"/>
+        <v>6.8461538461538449E-2</v>
+      </c>
+      <c r="HB7">
+        <f t="shared" si="35"/>
+        <v>0.10416666666666669</v>
+      </c>
     </row>
-    <row r="8" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B8">
         <v>1.5</v>
@@ -5664,10 +6004,54 @@
       <c r="GQ8">
         <v>10.708749999999998</v>
       </c>
+      <c r="GR8">
+        <f t="shared" si="25"/>
+        <v>0.72250000000000003</v>
+      </c>
+      <c r="GS8">
+        <f t="shared" si="26"/>
+        <v>1.8137500000000004</v>
+      </c>
+      <c r="GT8">
+        <f t="shared" si="27"/>
+        <v>0.49249999999999994</v>
+      </c>
+      <c r="GU8">
+        <f t="shared" si="28"/>
+        <v>9.1249999999999609E-2</v>
+      </c>
+      <c r="GV8">
+        <f t="shared" si="29"/>
+        <v>3.125</v>
+      </c>
+      <c r="GW8">
+        <f t="shared" si="30"/>
+        <v>10.75</v>
+      </c>
+      <c r="GX8" s="2">
+        <f t="shared" si="31"/>
+        <v>0.59601449275362317</v>
+      </c>
+      <c r="GY8" s="2">
+        <f t="shared" si="32"/>
+        <v>0.30978260869565216</v>
+      </c>
+      <c r="GZ8" s="2">
+        <f t="shared" si="33"/>
+        <v>9.420289855072464E-2</v>
+      </c>
+      <c r="HA8">
+        <f t="shared" si="34"/>
+        <v>0.12793650793650793</v>
+      </c>
+      <c r="HB8">
+        <f t="shared" si="35"/>
+        <v>0.11227941176470591</v>
+      </c>
     </row>
-    <row r="9" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B9" s="1">
         <v>1.25</v>
@@ -6263,10 +6647,54 @@
       <c r="GQ9">
         <v>11.661249999999999</v>
       </c>
+      <c r="GR9">
+        <f t="shared" si="25"/>
+        <v>1.0362500000000001</v>
+      </c>
+      <c r="GS9">
+        <f t="shared" si="26"/>
+        <v>1.1937500000000001</v>
+      </c>
+      <c r="GT9">
+        <f t="shared" si="27"/>
+        <v>0.11874999999999991</v>
+      </c>
+      <c r="GU9">
+        <f t="shared" si="28"/>
+        <v>-0.31875000000000009</v>
+      </c>
+      <c r="GV9">
+        <f t="shared" si="29"/>
+        <v>5.125</v>
+      </c>
+      <c r="GW9">
+        <f t="shared" si="30"/>
+        <v>5.125</v>
+      </c>
+      <c r="GX9" s="2">
+        <f t="shared" si="31"/>
+        <v>0.41556291390728478</v>
+      </c>
+      <c r="GY9" s="2">
+        <f t="shared" si="32"/>
+        <v>0.45033112582781459</v>
+      </c>
+      <c r="GZ9" s="2">
+        <f t="shared" si="33"/>
+        <v>0.13410596026490065</v>
+      </c>
+      <c r="HA9">
+        <f t="shared" si="34"/>
+        <v>9.7311827956989255E-2</v>
+      </c>
+      <c r="HB9">
+        <f t="shared" si="35"/>
+        <v>0.1123529411764706</v>
+      </c>
     </row>
-    <row r="10" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B10">
         <v>1.125</v>
@@ -6862,10 +7290,54 @@
       <c r="GQ10">
         <v>10.603749999999998</v>
       </c>
+      <c r="GR10">
+        <f t="shared" si="25"/>
+        <v>1.0087500000000003</v>
+      </c>
+      <c r="GS10">
+        <f t="shared" si="26"/>
+        <v>1.05125</v>
+      </c>
+      <c r="GT10">
+        <f t="shared" si="27"/>
+        <v>-7.3750000000000204E-2</v>
+      </c>
+      <c r="GU10">
+        <f t="shared" si="28"/>
+        <v>-0.14624999999999999</v>
+      </c>
+      <c r="GV10">
+        <f t="shared" si="29"/>
+        <v>5.625</v>
+      </c>
+      <c r="GW10">
+        <f t="shared" si="30"/>
+        <v>5.25</v>
+      </c>
+      <c r="GX10" s="2">
+        <f t="shared" si="31"/>
+        <v>0.45561139028475711</v>
+      </c>
+      <c r="GY10" s="2">
+        <f t="shared" si="32"/>
+        <v>0.41708542713567837</v>
+      </c>
+      <c r="GZ10" s="2">
+        <f t="shared" si="33"/>
+        <v>0.12730318257956449</v>
+      </c>
+      <c r="HA10">
+        <f t="shared" si="34"/>
+        <v>0.11282352941176473</v>
+      </c>
+      <c r="HB10">
+        <f t="shared" si="35"/>
+        <v>9.8602150537634409E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -7461,10 +7933,54 @@
       <c r="GQ11" s="1">
         <v>9.4</v>
       </c>
+      <c r="GR11">
+        <f t="shared" si="25"/>
+        <v>0.82000000000000017</v>
+      </c>
+      <c r="GS11">
+        <f t="shared" si="26"/>
+        <v>1.2114285714285715</v>
+      </c>
+      <c r="GT11">
+        <f t="shared" si="27"/>
+        <v>0.17999999999999983</v>
+      </c>
+      <c r="GU11">
+        <f t="shared" si="28"/>
+        <v>0.25142857142857133</v>
+      </c>
+      <c r="GV11">
+        <f t="shared" si="29"/>
+        <v>3.7142857142857135</v>
+      </c>
+      <c r="GW11">
+        <f t="shared" si="30"/>
+        <v>7.7142857142857153</v>
+      </c>
+      <c r="GX11" s="2">
+        <f t="shared" si="31"/>
+        <v>0.53302961275626426</v>
+      </c>
+      <c r="GY11" s="2">
+        <f t="shared" si="32"/>
+        <v>0.38496583143507973</v>
+      </c>
+      <c r="GZ11" s="2">
+        <f t="shared" si="33"/>
+        <v>8.2004555808656038E-2</v>
+      </c>
+      <c r="HA11">
+        <f t="shared" si="34"/>
+        <v>8.9687500000000017E-2</v>
+      </c>
+      <c r="HB11">
+        <f t="shared" si="35"/>
+        <v>9.2399999999999996E-2</v>
+      </c>
     </row>
-    <row r="12" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B12">
         <v>1.125</v>
@@ -8060,10 +8576,54 @@
       <c r="GQ12">
         <v>14.30125</v>
       </c>
+      <c r="GR12">
+        <f t="shared" si="25"/>
+        <v>1.1949999999999998</v>
+      </c>
+      <c r="GS12">
+        <f t="shared" si="26"/>
+        <v>1.0325000000000002</v>
+      </c>
+      <c r="GT12">
+        <f t="shared" si="27"/>
+        <v>-0.35499999999999998</v>
+      </c>
+      <c r="GU12">
+        <f t="shared" si="28"/>
+        <v>8.7499999999999689E-2</v>
+      </c>
+      <c r="GV12">
+        <f t="shared" si="29"/>
+        <v>7.25</v>
+      </c>
+      <c r="GW12">
+        <f t="shared" si="30"/>
+        <v>4.625</v>
+      </c>
+      <c r="GX12" s="2">
+        <f t="shared" si="31"/>
+        <v>0.35198555956678701</v>
+      </c>
+      <c r="GY12" s="2">
+        <f t="shared" si="32"/>
+        <v>0.48555956678700363</v>
+      </c>
+      <c r="GZ12" s="2">
+        <f t="shared" si="33"/>
+        <v>0.16245487364620939</v>
+      </c>
+      <c r="HA12">
+        <f t="shared" si="34"/>
+        <v>0.10666666666666666</v>
+      </c>
+      <c r="HB12">
+        <f t="shared" si="35"/>
+        <v>0.16617647058823534</v>
+      </c>
     </row>
-    <row r="13" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B13">
         <v>1.75</v>
@@ -8659,10 +9219,54 @@
       <c r="GQ13">
         <v>11.4625</v>
       </c>
+      <c r="GR13">
+        <f t="shared" si="25"/>
+        <v>0.97124999999999995</v>
+      </c>
+      <c r="GS13">
+        <f t="shared" si="26"/>
+        <v>0.98249999999999993</v>
+      </c>
+      <c r="GT13">
+        <f t="shared" si="27"/>
+        <v>0.77875000000000005</v>
+      </c>
+      <c r="GU13">
+        <f t="shared" si="28"/>
+        <v>0.32750000000000012</v>
+      </c>
+      <c r="GV13">
+        <f t="shared" si="29"/>
+        <v>4.75</v>
+      </c>
+      <c r="GW13">
+        <f t="shared" si="30"/>
+        <v>4.625</v>
+      </c>
+      <c r="GX13" s="2">
+        <f t="shared" si="31"/>
+        <v>0.50184501845018448</v>
+      </c>
+      <c r="GY13" s="2">
+        <f t="shared" si="32"/>
+        <v>0.39852398523985239</v>
+      </c>
+      <c r="GZ13" s="2">
+        <f t="shared" si="33"/>
+        <v>9.9630996309963096E-2</v>
+      </c>
+      <c r="HA13">
+        <f t="shared" si="34"/>
+        <v>8.1789473684210523E-2</v>
+      </c>
+      <c r="HB13">
+        <f t="shared" si="35"/>
+        <v>0.10307692307692307</v>
+      </c>
     </row>
-    <row r="14" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B14">
         <v>1.1428571428571428</v>
@@ -9258,10 +9862,54 @@
       <c r="GQ14">
         <v>10.705714285714285</v>
       </c>
+      <c r="GR14">
+        <f t="shared" si="25"/>
+        <v>0.75857142857142867</v>
+      </c>
+      <c r="GS14">
+        <f t="shared" si="26"/>
+        <v>1.6642857142857141</v>
+      </c>
+      <c r="GT14">
+        <f t="shared" si="27"/>
+        <v>0.38428571428571412</v>
+      </c>
+      <c r="GU14">
+        <f t="shared" si="28"/>
+        <v>8.4285714285714519E-2</v>
+      </c>
+      <c r="GV14">
+        <f t="shared" si="29"/>
+        <v>3.0000000000000004</v>
+      </c>
+      <c r="GW14">
+        <f t="shared" si="30"/>
+        <v>7.4285714285714288</v>
+      </c>
+      <c r="GX14" s="2">
+        <f t="shared" si="31"/>
+        <v>0.56623931623931612</v>
+      </c>
+      <c r="GY14" s="2">
+        <f t="shared" si="32"/>
+        <v>0.34401709401709402</v>
+      </c>
+      <c r="GZ14" s="2">
+        <f t="shared" si="33"/>
+        <v>8.9743589743589744E-2</v>
+      </c>
+      <c r="HA14">
+        <f t="shared" si="34"/>
+        <v>0.12348837209302327</v>
+      </c>
+      <c r="HB14">
+        <f t="shared" si="35"/>
+        <v>0.11490740740740739</v>
+      </c>
     </row>
-    <row r="15" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B15">
         <v>1.7142857142857142</v>
@@ -9857,10 +10505,54 @@
       <c r="GQ15">
         <v>12.202857142857143</v>
       </c>
+      <c r="GR15">
+        <f t="shared" si="25"/>
+        <v>1.1628571428571428</v>
+      </c>
+      <c r="GS15">
+        <f t="shared" si="26"/>
+        <v>1.1800000000000002</v>
+      </c>
+      <c r="GT15">
+        <f t="shared" si="27"/>
+        <v>0.11714285714285699</v>
+      </c>
+      <c r="GU15">
+        <f t="shared" si="28"/>
+        <v>0.24857142857142844</v>
+      </c>
+      <c r="GV15">
+        <f t="shared" si="29"/>
+        <v>7.8571428571428577</v>
+      </c>
+      <c r="GW15">
+        <f t="shared" si="30"/>
+        <v>5.8571428571428577</v>
+      </c>
+      <c r="GX15" s="2">
+        <f t="shared" si="31"/>
+        <v>0.37346938775510202</v>
+      </c>
+      <c r="GY15" s="2">
+        <f t="shared" si="32"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="GZ15" s="2">
+        <f t="shared" si="33"/>
+        <v>0.1979591836734694</v>
+      </c>
+      <c r="HA15">
+        <f t="shared" si="34"/>
+        <v>0.1075</v>
+      </c>
+      <c r="HB15">
+        <f t="shared" si="35"/>
+        <v>0.10325000000000001</v>
+      </c>
     </row>
-    <row r="16" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B16">
         <v>1.125</v>
@@ -10456,10 +11148,54 @@
       <c r="GQ16">
         <v>9.1787500000000009</v>
       </c>
+      <c r="GR16">
+        <f t="shared" si="25"/>
+        <v>0.78999999999999992</v>
+      </c>
+      <c r="GS16">
+        <f t="shared" si="26"/>
+        <v>1.30375</v>
+      </c>
+      <c r="GT16">
+        <f t="shared" si="27"/>
+        <v>-4.4999999999999929E-2</v>
+      </c>
+      <c r="GU16">
+        <f t="shared" si="28"/>
+        <v>-0.49374999999999991</v>
+      </c>
+      <c r="GV16">
+        <f t="shared" si="29"/>
+        <v>4.875</v>
+      </c>
+      <c r="GW16">
+        <f t="shared" si="30"/>
+        <v>7</v>
+      </c>
+      <c r="GX16" s="2">
+        <f t="shared" si="31"/>
+        <v>0.50338983050847452</v>
+      </c>
+      <c r="GY16" s="2">
+        <f t="shared" si="32"/>
+        <v>0.38474576271186439</v>
+      </c>
+      <c r="GZ16" s="2">
+        <f t="shared" si="33"/>
+        <v>0.11186440677966102</v>
+      </c>
+      <c r="HA16">
+        <f t="shared" si="34"/>
+        <v>0.12821917808219177</v>
+      </c>
+      <c r="HB16">
+        <f t="shared" si="35"/>
+        <v>0.12578947368421051</v>
+      </c>
     </row>
-    <row r="17" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B17">
         <v>1.25</v>
@@ -11055,10 +11791,54 @@
       <c r="GQ17">
         <v>9.7087500000000002</v>
       </c>
+      <c r="GR17">
+        <f t="shared" si="25"/>
+        <v>1.4824999999999999</v>
+      </c>
+      <c r="GS17">
+        <f t="shared" si="26"/>
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="GT17">
+        <f t="shared" si="27"/>
+        <v>-0.3274999999999999</v>
+      </c>
+      <c r="GU17">
+        <f t="shared" si="28"/>
+        <v>0.12999999999999989</v>
+      </c>
+      <c r="GV17">
+        <f t="shared" si="29"/>
+        <v>7.25</v>
+      </c>
+      <c r="GW17">
+        <f t="shared" si="30"/>
+        <v>4.625</v>
+      </c>
+      <c r="GX17" s="2">
+        <f t="shared" si="31"/>
+        <v>0.40589198036006546</v>
+      </c>
+      <c r="GY17" s="2">
+        <f t="shared" si="32"/>
+        <v>0.43207855973813419</v>
+      </c>
+      <c r="GZ17" s="2">
+        <f t="shared" si="33"/>
+        <v>0.16202945990180032</v>
+      </c>
+      <c r="HA17">
+        <f t="shared" si="34"/>
+        <v>0.10260162601626016</v>
+      </c>
+      <c r="HB17">
+        <f t="shared" si="35"/>
+        <v>0.16606060606060608</v>
+      </c>
     </row>
-    <row r="18" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -11654,10 +12434,54 @@
       <c r="GQ18">
         <v>9.2562499999999996</v>
       </c>
+      <c r="GR18">
+        <f t="shared" si="25"/>
+        <v>1.2850000000000001</v>
+      </c>
+      <c r="GS18">
+        <f t="shared" si="26"/>
+        <v>1.0975000000000001</v>
+      </c>
+      <c r="GT18">
+        <f t="shared" si="27"/>
+        <v>-0.47500000000000009</v>
+      </c>
+      <c r="GU18">
+        <f t="shared" si="28"/>
+        <v>0.15249999999999986</v>
+      </c>
+      <c r="GV18">
+        <f t="shared" si="29"/>
+        <v>6.375</v>
+      </c>
+      <c r="GW18">
+        <f t="shared" si="30"/>
+        <v>5.125</v>
+      </c>
+      <c r="GX18" s="2">
+        <f t="shared" si="31"/>
+        <v>0.50621669626998222</v>
+      </c>
+      <c r="GY18" s="2">
+        <f t="shared" si="32"/>
+        <v>0.35879218472468916</v>
+      </c>
+      <c r="GZ18" s="2">
+        <f t="shared" si="33"/>
+        <v>0.13499111900532859</v>
+      </c>
+      <c r="HA18">
+        <f t="shared" si="34"/>
+        <v>0.11800000000000001</v>
+      </c>
+      <c r="HB18">
+        <f t="shared" si="35"/>
+        <v>8.607843137254903E-2</v>
+      </c>
     </row>
-    <row r="19" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B19">
         <v>1.625</v>
@@ -12253,10 +13077,54 @@
       <c r="GQ19">
         <v>11.954999999999998</v>
       </c>
+      <c r="GR19">
+        <f t="shared" si="25"/>
+        <v>1.3225000000000002</v>
+      </c>
+      <c r="GS19">
+        <f t="shared" si="26"/>
+        <v>0.99000000000000021</v>
+      </c>
+      <c r="GT19">
+        <f t="shared" si="27"/>
+        <v>0.2074999999999998</v>
+      </c>
+      <c r="GU19">
+        <f t="shared" si="28"/>
+        <v>6.999999999999984E-2</v>
+      </c>
+      <c r="GV19">
+        <f t="shared" si="29"/>
+        <v>7.25</v>
+      </c>
+      <c r="GW19">
+        <f t="shared" si="30"/>
+        <v>5.25</v>
+      </c>
+      <c r="GX19" s="2">
+        <f t="shared" si="31"/>
+        <v>0.48345588235294118</v>
+      </c>
+      <c r="GY19" s="2">
+        <f t="shared" si="32"/>
+        <v>0.33823529411764708</v>
+      </c>
+      <c r="GZ19" s="2">
+        <f t="shared" si="33"/>
+        <v>0.17830882352941177</v>
+      </c>
+      <c r="HA19">
+        <f t="shared" si="34"/>
+        <v>0.10800000000000001</v>
+      </c>
+      <c r="HB19">
+        <f t="shared" si="35"/>
+        <v>9.3465346534653479E-2</v>
+      </c>
     </row>
-    <row r="20" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B20">
         <v>1.125</v>
@@ -12852,10 +13720,54 @@
       <c r="GQ20">
         <v>13.56625</v>
       </c>
+      <c r="GR20">
+        <f t="shared" si="25"/>
+        <v>1.4350000000000003</v>
+      </c>
+      <c r="GS20">
+        <f t="shared" si="26"/>
+        <v>0.85750000000000015</v>
+      </c>
+      <c r="GT20">
+        <f t="shared" si="27"/>
+        <v>-0.31000000000000028</v>
+      </c>
+      <c r="GU20">
+        <f t="shared" si="28"/>
+        <v>0.29749999999999988</v>
+      </c>
+      <c r="GV20">
+        <f t="shared" si="29"/>
+        <v>7.125</v>
+      </c>
+      <c r="GW20">
+        <f t="shared" si="30"/>
+        <v>4.625</v>
+      </c>
+      <c r="GX20" s="2">
+        <f t="shared" si="31"/>
+        <v>0.37453874538745385</v>
+      </c>
+      <c r="GY20" s="2">
+        <f t="shared" si="32"/>
+        <v>0.44280442804428044</v>
+      </c>
+      <c r="GZ20" s="2">
+        <f t="shared" si="33"/>
+        <v>0.18265682656826568</v>
+      </c>
+      <c r="HA20">
+        <f t="shared" si="34"/>
+        <v>0.10159292035398232</v>
+      </c>
+      <c r="HB20">
+        <f t="shared" si="35"/>
+        <v>8.8604651162790704E-2</v>
+      </c>
     </row>
-    <row r="21" spans="1:199" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:210" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B21">
         <v>1.25</v>
@@ -13450,6 +14362,50 @@
       </c>
       <c r="GQ21">
         <v>12.62875</v>
+      </c>
+      <c r="GR21">
+        <f t="shared" si="25"/>
+        <v>1.2200000000000002</v>
+      </c>
+      <c r="GS21">
+        <f t="shared" si="26"/>
+        <v>0.87250000000000005</v>
+      </c>
+      <c r="GT21">
+        <f t="shared" si="27"/>
+        <v>-6.5000000000000169E-2</v>
+      </c>
+      <c r="GU21">
+        <f t="shared" si="28"/>
+        <v>2.4999999999999467E-3</v>
+      </c>
+      <c r="GV21">
+        <f t="shared" si="29"/>
+        <v>5.75</v>
+      </c>
+      <c r="GW21">
+        <f t="shared" si="30"/>
+        <v>5.75</v>
+      </c>
+      <c r="GX21" s="2">
+        <f t="shared" si="31"/>
+        <v>0.44919786096256686</v>
+      </c>
+      <c r="GY21" s="2">
+        <f t="shared" si="32"/>
+        <v>0.40641711229946526</v>
+      </c>
+      <c r="GZ21" s="2">
+        <f t="shared" si="33"/>
+        <v>0.14438502673796791</v>
+      </c>
+      <c r="HA21">
+        <f t="shared" si="34"/>
+        <v>0.1119148936170213</v>
+      </c>
+      <c r="HB21">
+        <f t="shared" si="35"/>
+        <v>6.9800000000000001E-2</v>
       </c>
     </row>
   </sheetData>
